--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INVEREADY GIPUZKOA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INVEREADY GIPUZKOA.xlsx
@@ -565,13 +565,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>82.7161</v>
+        <v>63.3625</v>
       </c>
       <c r="E2" t="n">
-        <v>45.2539</v>
+        <v>34.2116</v>
       </c>
       <c r="F2" t="n">
-        <v>37.4626</v>
+        <v>29.1508</v>
       </c>
       <c r="G2" t="n">
         <v>50.321</v>
@@ -610,13 +610,13 @@
         <v>35.453</v>
       </c>
       <c r="S2" t="n">
-        <v>40.9215</v>
+        <v>21.5679</v>
       </c>
       <c r="T2" t="n">
-        <v>19.1204</v>
+        <v>8.078100000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>21.8011</v>
+        <v>13.4898</v>
       </c>
       <c r="V2" t="n">
         <v>13.2246</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>49.3912</v>
+        <v>48.8339</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6355</v>
+        <v>18.8199</v>
       </c>
       <c r="F3" t="n">
-        <v>20.7565</v>
+        <v>30.014</v>
       </c>
       <c r="G3" t="n">
-        <v>9.2652</v>
+        <v>10.096</v>
       </c>
       <c r="H3" t="n">
-        <v>10.2669</v>
+        <v>18.1412</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0021</v>
+        <v>-8.045199999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>21.2949</v>
+        <v>13.9027</v>
       </c>
       <c r="K3" t="n">
-        <v>12.6216</v>
+        <v>16.2614</v>
       </c>
       <c r="L3" t="n">
-        <v>8.673100000000002</v>
+        <v>-2.358900000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.0303</v>
+        <v>-3.8066</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3547</v>
+        <v>1.8797</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.6754</v>
+        <v>-5.685700000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>16.0954</v>
+        <v>25.4478</v>
       </c>
       <c r="Q3" t="n">
-        <v>-31.5383</v>
+        <v>-12.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>47.6338</v>
+        <v>38.2807</v>
       </c>
       <c r="S3" t="n">
-        <v>27.0488</v>
+        <v>6.8065</v>
       </c>
       <c r="T3" t="n">
-        <v>19.0001</v>
+        <v>3.9541</v>
       </c>
       <c r="U3" t="n">
-        <v>8.048400000000001</v>
+        <v>2.8526</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.0176</v>
+        <v>6.483600000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>19.8781</v>
+        <v>13.7962</v>
       </c>
       <c r="X3" t="n">
-        <v>-22.8958</v>
+        <v>-7.3127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>44.7642</v>
+        <v>38.1383</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9972</v>
+        <v>19.0452</v>
       </c>
       <c r="F4" t="n">
-        <v>30.7666</v>
+        <v>19.0925</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9615</v>
+        <v>9.2652</v>
       </c>
       <c r="H4" t="n">
-        <v>16.7651</v>
+        <v>10.2669</v>
       </c>
       <c r="I4" t="n">
-        <v>-14.8035</v>
+        <v>-1.0021</v>
       </c>
       <c r="J4" t="n">
-        <v>7.382400000000001</v>
+        <v>21.2949</v>
       </c>
       <c r="K4" t="n">
-        <v>14.5474</v>
+        <v>12.6216</v>
       </c>
       <c r="L4" t="n">
-        <v>-7.165399999999999</v>
+        <v>8.673100000000002</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.4209</v>
+        <v>-12.0303</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2175</v>
+        <v>-2.3547</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.6384</v>
+        <v>-9.6754</v>
       </c>
       <c r="P4" t="n">
-        <v>-26.3182</v>
+        <v>16.0954</v>
       </c>
       <c r="Q4" t="n">
-        <v>-66.3398</v>
+        <v>-31.5383</v>
       </c>
       <c r="R4" t="n">
-        <v>40.0208</v>
+        <v>47.6338</v>
       </c>
       <c r="S4" t="n">
-        <v>61.2395</v>
+        <v>15.7955</v>
       </c>
       <c r="T4" t="n">
-        <v>45.8236</v>
+        <v>9.410499999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>15.4158</v>
+        <v>6.3845</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8815</v>
+        <v>-3.0176</v>
       </c>
       <c r="W4" t="n">
-        <v>27.131</v>
+        <v>19.8781</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.2494</v>
+        <v>-22.8958</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>32.58</v>
+        <v>27.3543</v>
       </c>
       <c r="E5" t="n">
-        <v>9.316800000000001</v>
+        <v>19.8309</v>
       </c>
       <c r="F5" t="n">
-        <v>23.2636</v>
+        <v>7.523300000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>10.096</v>
+        <v>46.5685</v>
       </c>
       <c r="H5" t="n">
-        <v>18.1412</v>
+        <v>38.0928</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.045199999999999</v>
+        <v>8.4754</v>
       </c>
       <c r="J5" t="n">
-        <v>13.9027</v>
+        <v>51.0226</v>
       </c>
       <c r="K5" t="n">
-        <v>16.2614</v>
+        <v>36.2859</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.358900000000001</v>
+        <v>14.7368</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.8066</v>
+        <v>-4.4544</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8797</v>
+        <v>1.8071</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.685700000000001</v>
+        <v>-6.2611</v>
       </c>
       <c r="P5" t="n">
-        <v>25.4478</v>
+        <v>-10.4404</v>
       </c>
       <c r="Q5" t="n">
-        <v>-12.8326</v>
+        <v>-42.8488</v>
       </c>
       <c r="R5" t="n">
-        <v>38.2807</v>
+        <v>32.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>-9.4475</v>
+        <v>-1.4614</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.549300000000001</v>
+        <v>-1.9848</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.8986</v>
+        <v>0.5239</v>
       </c>
       <c r="V5" t="n">
-        <v>6.483600000000001</v>
+        <v>-7.3121</v>
       </c>
       <c r="W5" t="n">
-        <v>13.7962</v>
+        <v>13.6425</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.3127</v>
+        <v>-20.9546</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>16.2667</v>
+        <v>20.2847</v>
       </c>
       <c r="E6" t="n">
-        <v>14.0557</v>
+        <v>14.7331</v>
       </c>
       <c r="F6" t="n">
-        <v>2.210899999999999</v>
+        <v>5.551399999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>46.5685</v>
+        <v>34.6553</v>
       </c>
       <c r="H6" t="n">
-        <v>38.0928</v>
+        <v>21.6353</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4754</v>
+        <v>13.0201</v>
       </c>
       <c r="J6" t="n">
-        <v>51.0226</v>
+        <v>48.1631</v>
       </c>
       <c r="K6" t="n">
-        <v>36.2859</v>
+        <v>23.0589</v>
       </c>
       <c r="L6" t="n">
-        <v>14.7368</v>
+        <v>25.1048</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.4544</v>
+        <v>-13.5078</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8071</v>
+        <v>-1.4235</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.2611</v>
+        <v>-12.084</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.4404</v>
+        <v>-8.9178</v>
       </c>
       <c r="Q6" t="n">
-        <v>-42.8488</v>
+        <v>-49.5913</v>
       </c>
       <c r="R6" t="n">
-        <v>32.4087</v>
+        <v>40.6738</v>
       </c>
       <c r="S6" t="n">
-        <v>-12.5488</v>
+        <v>-0.2590000000000005</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.7605</v>
+        <v>1.41</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.7883</v>
+        <v>-1.6685</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.3121</v>
+        <v>-5.1937</v>
       </c>
       <c r="W6" t="n">
-        <v>13.6425</v>
+        <v>14.7517</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.9546</v>
+        <v>-19.9454</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>12.2191</v>
+        <v>12.7501</v>
       </c>
       <c r="E7" t="n">
-        <v>25.5592</v>
+        <v>-12.803</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.3403</v>
+        <v>25.553</v>
       </c>
       <c r="G7" t="n">
-        <v>21.8843</v>
+        <v>1.9615</v>
       </c>
       <c r="H7" t="n">
-        <v>20.5111</v>
+        <v>16.7651</v>
       </c>
       <c r="I7" t="n">
-        <v>1.373499999999999</v>
+        <v>-14.8035</v>
       </c>
       <c r="J7" t="n">
-        <v>38.7523</v>
+        <v>7.382400000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>21.118</v>
+        <v>14.5474</v>
       </c>
       <c r="L7" t="n">
-        <v>17.6339</v>
+        <v>-7.165399999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.868</v>
+        <v>-5.4209</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6067999999999998</v>
+        <v>2.2175</v>
       </c>
       <c r="O7" t="n">
-        <v>-16.2612</v>
+        <v>-7.6384</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.000200000000000089</v>
+        <v>-26.3182</v>
       </c>
       <c r="Q7" t="n">
-        <v>-36.7584</v>
+        <v>-66.3398</v>
       </c>
       <c r="R7" t="n">
-        <v>36.7582</v>
+        <v>40.0208</v>
       </c>
       <c r="S7" t="n">
-        <v>7.5508</v>
+        <v>29.2254</v>
       </c>
       <c r="T7" t="n">
-        <v>5.6074</v>
+        <v>19.0235</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9434</v>
+        <v>10.2025</v>
       </c>
       <c r="V7" t="n">
-        <v>-17.2167</v>
+        <v>7.8815</v>
       </c>
       <c r="W7" t="n">
-        <v>17.9581</v>
+        <v>27.131</v>
       </c>
       <c r="X7" t="n">
-        <v>-35.1742</v>
+        <v>-19.2494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>2.223199999999999</v>
+        <v>11.809</v>
       </c>
       <c r="E8" t="n">
-        <v>4.696899999999999</v>
+        <v>24.24</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4736</v>
+        <v>-12.4308</v>
       </c>
       <c r="G8" t="n">
-        <v>34.6553</v>
+        <v>21.8843</v>
       </c>
       <c r="H8" t="n">
-        <v>21.6353</v>
+        <v>20.5111</v>
       </c>
       <c r="I8" t="n">
-        <v>13.0201</v>
+        <v>1.373499999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>48.1631</v>
+        <v>38.7523</v>
       </c>
       <c r="K8" t="n">
-        <v>23.0589</v>
+        <v>21.118</v>
       </c>
       <c r="L8" t="n">
-        <v>25.1048</v>
+        <v>17.6339</v>
       </c>
       <c r="M8" t="n">
-        <v>-13.5078</v>
+        <v>-16.868</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4235</v>
+        <v>-0.6067999999999998</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.084</v>
+        <v>-16.2612</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.9178</v>
+        <v>-0.000200000000000089</v>
       </c>
       <c r="Q8" t="n">
-        <v>-49.5913</v>
+        <v>-36.7584</v>
       </c>
       <c r="R8" t="n">
-        <v>40.6738</v>
+        <v>36.7582</v>
       </c>
       <c r="S8" t="n">
-        <v>-18.3206</v>
+        <v>7.1412</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.6267</v>
+        <v>4.2879</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.6937</v>
+        <v>2.8532</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.1937</v>
+        <v>-17.2167</v>
       </c>
       <c r="W8" t="n">
-        <v>14.7517</v>
+        <v>17.9581</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.9454</v>
+        <v>-35.1742</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7451</v>
+        <v>3.5704</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7451</v>
+        <v>-5.737500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>9.307700000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8.388300000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6.6979</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.6904</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>17.8168</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8.3443</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9.4725</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-9.428699999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.6466</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-7.7817</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-11.528</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-45.8937</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>34.3655</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7451</v>
+        <v>0.4008</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7451</v>
+        <v>1.959</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1.5579</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.3089</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>20.3807</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-14.072</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0943</v>
+        <v>2.8983</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0008</v>
+        <v>-7.745399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09350000000000003</v>
+        <v>10.6438</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4471000000000001</v>
+        <v>-0.7265999999999988</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0432</v>
+        <v>3.8474</v>
       </c>
       <c r="I10" t="n">
-        <v>0.596</v>
+        <v>-4.5739</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7269</v>
+        <v>16.2565</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7269</v>
+        <v>6.744899999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9.5115</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2796</v>
+        <v>-16.9832</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3165</v>
+        <v>-2.8973</v>
       </c>
       <c r="O10" t="n">
-        <v>0.596</v>
+        <v>-14.0857</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>5.8724</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-35.2358</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>41.1085</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2998</v>
+        <v>3.1742</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.4766000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0259</v>
+        <v>3.651</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-5.4221</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>11.7109</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-17.133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.884</v>
+        <v>0.298</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.004799999999999</v>
+        <v>0.298</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8794</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5256</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4632</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0623</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3545</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2430000000000001</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1117</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.171</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2205</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04929999999999993</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.48</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1326</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6835000000000001</v>
+        <v>0.298</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0489</v>
+        <v>0.298</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3655</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.6945</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7808999999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.4753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.3914</v>
+        <v>-0.8409</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.2261</v>
+        <v>-0.9323</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8348</v>
+        <v>0.09139999999999993</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8209</v>
+        <v>-0.4471000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>9.9458</v>
+        <v>-1.0432</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.7675</v>
+        <v>0.596</v>
       </c>
       <c r="J12" t="n">
-        <v>3.570799999999999</v>
+        <v>-0.7269</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7724</v>
+        <v>-0.7269</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.201899999999999</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.392099999999999</v>
+        <v>0.2796</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8265999999999999</v>
+        <v>-0.3165</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.5655</v>
+        <v>0.596</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6526</v>
+        <v>0.2175</v>
       </c>
       <c r="Q12" t="n">
-        <v>-24.578</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>23.9254</v>
+        <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2794</v>
+        <v>-0.04620000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>4.045</v>
+        <v>-0.2055</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2344999999999998</v>
+        <v>0.1593</v>
       </c>
       <c r="V12" t="n">
-        <v>-14.1967</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7364</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.933</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.2482</v>
+        <v>-7.0561</v>
       </c>
       <c r="E13" t="n">
-        <v>-24.573</v>
+        <v>-19.2988</v>
       </c>
       <c r="F13" t="n">
-        <v>9.3247</v>
+        <v>12.2428</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4265</v>
@@ -1468,13 +1468,13 @@
         <v>20.8803</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9932</v>
+        <v>9.1859</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0393</v>
+        <v>3.2351</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0326</v>
+        <v>5.9507</v>
       </c>
       <c r="V13" t="n">
         <v>1.7154</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.2783</v>
+        <v>-8.2181</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.2827</v>
+        <v>-4.6932</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0045</v>
+        <v>-3.5248</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7265999999999988</v>
+        <v>-4.5256</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8474</v>
+        <v>-1.4632</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.5739</v>
+        <v>-3.0623</v>
       </c>
       <c r="J14" t="n">
-        <v>16.2565</v>
+        <v>-3.3545</v>
       </c>
       <c r="K14" t="n">
-        <v>6.744899999999999</v>
+        <v>-0.2430000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>9.5115</v>
+        <v>-3.1117</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.9832</v>
+        <v>-1.171</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.8973</v>
+        <v>-1.2205</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.0857</v>
+        <v>0.04929999999999993</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8724</v>
+        <v>0.6525000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-35.2358</v>
+        <v>-3.48</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1085</v>
+        <v>4.1326</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.0021</v>
+        <v>0.3494000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.0143</v>
+        <v>1.3604</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.011</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.4221</v>
+        <v>-4.6945</v>
       </c>
       <c r="W14" t="n">
-        <v>11.7109</v>
+        <v>0.7808999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.133</v>
+        <v>-5.4753</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.3462</v>
+        <v>-8.3743</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.2952</v>
+        <v>-11.9202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9488999999999999</v>
+        <v>3.5455</v>
       </c>
       <c r="G15" t="n">
-        <v>8.388300000000001</v>
+        <v>-2.8209</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6979</v>
+        <v>9.9458</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6904</v>
+        <v>-12.7675</v>
       </c>
       <c r="J15" t="n">
-        <v>17.8168</v>
+        <v>3.570799999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>8.3443</v>
+        <v>10.7724</v>
       </c>
       <c r="L15" t="n">
-        <v>9.4725</v>
+        <v>-7.201899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.428699999999999</v>
+        <v>-6.392099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6466</v>
+        <v>-0.8265999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.7817</v>
+        <v>-5.5655</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.528</v>
+        <v>-0.6526</v>
       </c>
       <c r="Q15" t="n">
-        <v>-45.8937</v>
+        <v>-24.578</v>
       </c>
       <c r="R15" t="n">
-        <v>34.3655</v>
+        <v>23.9254</v>
       </c>
       <c r="S15" t="n">
-        <v>-19.5157</v>
+        <v>9.2963</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.599400000000001</v>
+        <v>7.351</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.9169</v>
+        <v>1.9455</v>
       </c>
       <c r="V15" t="n">
-        <v>6.3089</v>
+        <v>-14.1967</v>
       </c>
       <c r="W15" t="n">
-        <v>20.3807</v>
+        <v>1.7364</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.072</v>
+        <v>-15.933</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-22.066</v>
+        <v>-18.5277</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.5815</v>
+        <v>-14.4507</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.484500000000001</v>
+        <v>-4.0769</v>
       </c>
       <c r="G16" t="n">
         <v>-6.3575</v>
@@ -1702,13 +1702,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.3976</v>
+        <v>0.1407</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.1377</v>
+        <v>-0.007099999999999995</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2599</v>
+        <v>0.1476999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.7395000000000005</v>
@@ -1735,13 +1735,13 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>149.5972</v>
+        <v>186.2824</v>
       </c>
       <c r="E17" t="n">
-        <v>42.29619999999997</v>
+        <v>53.59760000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>107.3018</v>
+        <v>132.6837</v>
       </c>
       <c r="G17" t="n">
         <v>166.8359</v>
@@ -1750,22 +1750,22 @@
         <v>204.3104</v>
       </c>
       <c r="I17" t="n">
-        <v>-37.47560000000001</v>
+        <v>-37.4756</v>
       </c>
       <c r="J17" t="n">
-        <v>269.3566999999999</v>
+        <v>269.3567</v>
       </c>
       <c r="K17" t="n">
         <v>211.3746</v>
       </c>
       <c r="L17" t="n">
-        <v>57.9804</v>
+        <v>57.98040000000001</v>
       </c>
       <c r="M17" t="n">
         <v>-102.5227</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.0645</v>
+        <v>-7.064500000000001</v>
       </c>
       <c r="O17" t="n">
         <v>-95.4563</v>
@@ -1780,13 +1780,13 @@
         <v>405.6464</v>
       </c>
       <c r="S17" t="n">
-        <v>64.92970000000001</v>
+        <v>101.6152</v>
       </c>
       <c r="T17" t="n">
-        <v>46.38930000000001</v>
+        <v>57.6936</v>
       </c>
       <c r="U17" t="n">
-        <v>18.53859999999999</v>
+        <v>43.9233</v>
       </c>
       <c r="V17" t="n">
         <v>-21.2649</v>
